--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>Fecha:</t>
+  </si>
+  <si>
+    <t>24/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -843,8 +846,8 @@
       <c r="H8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
-        <v>45770.0</v>
+      <c r="I8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">
@@ -860,11 +863,11 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="15">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -887,23 +890,23 @@
     <row r="12" spans="1:10" customHeight="1" ht="15">
       <c r="A12" s="2"/>
       <c r="B12" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="18"/>
     </row>
@@ -920,7 +923,7 @@
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="15">
       <c r="A14" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -966,24 +969,24 @@
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="15">
       <c r="A18" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="22"/>
     </row>
@@ -992,17 +995,17 @@
         <v>1</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="38"/>
       <c r="F19" s="38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
@@ -1013,17 +1016,17 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1034,17 +1037,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1055,17 +1058,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1076,17 +1079,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1097,7 +1100,7 @@
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
       <c r="D24" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -1129,7 +1132,7 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -1153,7 +1156,7 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -1166,7 +1169,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1179,7 +1182,7 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1192,7 +1195,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="24.05">
       <c r="A32" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -1206,7 +1209,7 @@
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="27">
       <c r="A33" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="39">
       <c r="A35" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
@@ -1266,14 +1269,14 @@
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="32"/>
       <c r="B38" s="34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H38" s="35"/>
       <c r="I38" s="35"/>
@@ -1283,7 +1286,7 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -1316,7 +1319,7 @@
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
       <c r="B42" s="34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>
@@ -1332,7 +1335,7 @@
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>24/04/2025</t>
+    <t>28/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>28/04/2025</t>
+    <t>30/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Supervisor TI</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Auxiliar de Supervision</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>08/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>08/05/2025</t>
+    <t>19/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -86,6 +86,15 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>wertyuiop</t>
+  </si>
+  <si>
     <t>Teclado</t>
   </si>
   <si>
@@ -171,12 +180,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Auxiliar de Supervision</t>
   </si>
 </sst>
 </file>
@@ -1004,8 +1007,8 @@
         <v>24</v>
       </c>
       <c r="E19" s="38"/>
-      <c r="F19" s="38" t="s">
-        <v>25</v>
+      <c r="F19" s="38">
+        <v>214965856</v>
       </c>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
@@ -1016,10 +1019,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>26</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D20" s="38" t="s">
         <v>27</v>
@@ -1040,14 +1043,14 @@
         <v>29</v>
       </c>
       <c r="C21" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>30</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>31</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1058,17 +1061,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="D22" s="38" t="s">
         <v>34</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1079,10 +1082,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>38</v>
@@ -1096,80 +1099,88 @@
       <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22" t="s">
+      <c r="A24" s="38">
+        <v>6</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="C24" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1182,7 +1193,7 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1193,171 +1204,173 @@
       <c r="H31" s="28"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A32" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="27">
-      <c r="A33" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="39">
-      <c r="A35" s="31" t="s">
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A33" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="27">
+      <c r="A34" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="39">
+      <c r="A36" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="33"/>
       <c r="I37" s="33"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="32"/>
-      <c r="B38" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
-        <v>50</v>
-      </c>
+      <c r="A39" s="32"/>
+      <c r="B39" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="G39" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="36" t="s">
+        <v>53</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="34" t="str">
-        <f>C10</f>
-        <v>Alan Bauza Valdez</v>
-      </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="34" t="str">
+        <f>C10</f>
+        <v>Alan Bauza Valdez</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="34" t="str">
         <f>C12</f>
         <v>Supervisor Operaciones</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
@@ -1366,20 +1379,31 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1398,23 +1422,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G39:I39"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1433,7 +1457,10 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H19:I25"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>19/05/2025</t>
+    <t>02/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -152,6 +152,18 @@
     <t>DVZ-VH-TI-00098</t>
   </si>
   <si>
+    <t>Adaptador de Corriente</t>
+  </si>
+  <si>
+    <t>Polycom</t>
+  </si>
+  <si>
+    <t>sdwgyedhtr</t>
+  </si>
+  <si>
+    <t>FUYFG</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -180,6 +192,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1133,67 +1151,75 @@
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1206,7 +1232,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1217,171 +1243,173 @@
       <c r="H32" s="28"/>
       <c r="I32" s="28"/>
     </row>
-    <row r="33" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A33" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="27">
-      <c r="A34" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="39">
-      <c r="A36" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A34" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="27">
+      <c r="A35" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="39">
+      <c r="A37" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="2"/>
+      <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
       <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="G38" s="33"/>
       <c r="H38" s="33"/>
       <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="32"/>
-      <c r="B39" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="36" t="s">
-        <v>53</v>
-      </c>
+      <c r="A40" s="32"/>
+      <c r="B40" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="G40" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="36" t="s">
+        <v>57</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
-        <f>C10</f>
-        <v>Alan Bauza Valdez</v>
-      </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
       <c r="B44" s="34" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="34" t="str">
+        <f>C10</f>
+        <v>Alan Bauza Valdez</v>
+      </c>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="34" t="str">
         <f>C12</f>
         <v>Supervisor Operaciones</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
@@ -1390,20 +1418,31 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="32"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1422,23 +1461,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G40:I40"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="G44:I44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="G45:I45"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1460,7 +1499,10 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H19:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H19:I26"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>19/05/2025</t>
+    <t>02/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Tampico</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Rednar García Harcía</t>
+  </si>
+  <si>
+    <t>Auxiliar Predictivo</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1349,7 @@
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -1359,7 +1365,7 @@
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
       <c r="B44" s="34" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>02/06/2025</t>
+    <t>04/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -150,18 +150,6 @@
   </si>
   <si>
     <t>DVZ-VH-TI-00098</t>
-  </si>
-  <si>
-    <t>Adaptador de Corriente</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>sdwgyedhtr</t>
-  </si>
-  <si>
-    <t>FUYFG</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1151,75 +1139,67 @@
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="38">
-        <v>7</v>
-      </c>
-      <c r="B26" s="38" t="s">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="15">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="15">
+      <c r="A28" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="15">
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
+      <c r="A30" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1232,7 +1212,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="28" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1243,173 +1223,171 @@
       <c r="H32" s="28"/>
       <c r="I32" s="28"/>
     </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A34" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="27">
-      <c r="A35" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="39">
-      <c r="A37" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
+    <row r="33" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A33" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="27">
+      <c r="A34" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="39">
+      <c r="A36" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="15">
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="32"/>
+      <c r="A38" s="2"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
       <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="33"/>
+      <c r="G38" s="2"/>
       <c r="H38" s="33"/>
       <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
+      <c r="G39" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="32"/>
-      <c r="B40" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="36" t="s">
+        <v>53</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="36" t="s">
-        <v>57</v>
-      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="B43" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="G43" s="34" t="str">
+        <f>C10</f>
+        <v>Alan Bauza Valdez</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
       <c r="B44" s="34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="34" t="str">
-        <f>C10</f>
-        <v>Alan Bauza Valdez</v>
+        <f>C12</f>
+        <v>Supervisor Operaciones</v>
       </c>
       <c r="H44" s="34"/>
       <c r="I44" s="34"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
-      <c r="B45" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="34" t="str">
-        <f>C12</f>
-        <v>Supervisor Operaciones</v>
-      </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
@@ -1418,31 +1396,20 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1461,23 +1428,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="G43:I43"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="G44:I44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="G45:I45"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1499,10 +1466,7 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H19:I26"/>
+    <mergeCell ref="H19:I25"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>04/06/2025</t>
+    <t>12/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -95,6 +95,9 @@
     <t>wertyuiop</t>
   </si>
   <si>
+    <t>asdasdas</t>
+  </si>
+  <si>
     <t>Teclado</t>
   </si>
   <si>
@@ -182,10 +185,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1020,9 @@
         <v>214965856</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>25</v>
+      </c>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -1025,17 +1030,17 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1046,17 +1051,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1067,17 +1072,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1088,17 +1093,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1109,17 +1114,17 @@
         <v>6</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1130,7 +1135,7 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -1162,7 +1167,7 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -1186,7 +1191,7 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -1199,7 +1204,7 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1212,7 +1217,7 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1225,7 +1230,7 @@
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="24.05">
       <c r="A33" s="29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33" s="29"/>
       <c r="C33" s="29"/>
@@ -1239,7 +1244,7 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="27">
       <c r="A34" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1263,7 +1268,7 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="39">
       <c r="A36" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
@@ -1299,14 +1304,14 @@
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="32"/>
       <c r="B39" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H39" s="35"/>
       <c r="I39" s="35"/>
@@ -1316,7 +1321,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -1349,7 +1354,7 @@
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -1365,7 +1370,7 @@
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
       <c r="B44" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -95,9 +95,6 @@
     <t>wertyuiop</t>
   </si>
   <si>
-    <t>asdasdas</t>
-  </si>
-  <si>
     <t>Teclado</t>
   </si>
   <si>
@@ -155,6 +152,18 @@
     <t>DVZ-VH-TI-00098</t>
   </si>
   <si>
+    <t xml:space="preserve">Adaptador de Puerto  </t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>xctvgybij</t>
+  </si>
+  <si>
+    <t>DRFTGYUHJIPKO</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -185,10 +194,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1020,9 +1029,7 @@
         <v>214965856</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
-        <v>25</v>
-      </c>
+      <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -1030,17 +1037,17 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="D20" s="38" t="s">
         <v>27</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>28</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1051,17 +1058,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>30</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>31</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1072,17 +1079,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="D22" s="38" t="s">
         <v>34</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1093,17 +1100,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="D23" s="38" t="s">
         <v>38</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>39</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1114,17 +1121,17 @@
         <v>6</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>41</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>42</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1135,7 +1142,7 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -1144,80 +1151,96 @@
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
+      <c r="A27" s="38">
+        <v>8</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="A30" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1228,23 +1251,22 @@
       <c r="H32" s="28"/>
       <c r="I32" s="28"/>
     </row>
-    <row r="33" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A33" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="27">
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1255,96 +1277,101 @@
       <c r="H34" s="28"/>
       <c r="I34" s="28"/>
     </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="39">
-      <c r="A36" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
+    <row r="35" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A35" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="27">
+      <c r="A36" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="2"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="39">
+      <c r="A38" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="32"/>
-      <c r="B39" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="36" t="s">
-        <v>54</v>
-      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
+      <c r="G41" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="D42" s="36" t="s">
+        <v>57</v>
+      </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -1353,68 +1380,90 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="34" t="str">
         <f>C10</f>
         <v>Alan Bauza Valdez</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="34" t="str">
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+    </row>
+    <row r="46" spans="1:10" customHeight="1" ht="15">
+      <c r="A46" s="2"/>
+      <c r="B46" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="34" t="str">
         <f>C12</f>
         <v>Supervisor Operaciones</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-    </row>
-    <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="32"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1433,23 +1482,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="G46:I46"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1471,7 +1520,13 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H19:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H19:I27"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>12/06/2025</t>
+    <t>16/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>16/06/2025</t>
+    <t>19/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,154 +41,160 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>25/06/2025</t>
+    <t>01/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Región:</t>
+  </si>
+  <si>
+    <t>Ubicación:</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
+    <t>MODELO</t>
+  </si>
+  <si>
+    <t>NUMERO DE SERIE</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>wertyuiop</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>KB216T</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LV-A04</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>MS116T1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-08Y0</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>23-08-69698</t>
+  </si>
+  <si>
+    <t>Impresora</t>
+  </si>
+  <si>
+    <t>EPSON</t>
+  </si>
+  <si>
+    <t>EconTank L6270</t>
+  </si>
+  <si>
+    <t>X8G5011801</t>
+  </si>
+  <si>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>6TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adaptador de Puerto  </t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>xctvgybij</t>
+  </si>
+  <si>
+    <t>DRFTGYUHJIPKO</t>
+  </si>
+  <si>
+    <t>Adaptador de Corriente</t>
+  </si>
+  <si>
+    <t>YIGUOOIUHGOUB</t>
+  </si>
+  <si>
+    <t>GVOUIUOIUUGUOOU</t>
+  </si>
+  <si>
+    <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
+  </si>
+  <si>
+    <t>1. El uso correcto del equipo asignado.</t>
+  </si>
+  <si>
+    <t>2. Permitir realizar la auditoría y mantenimiento programado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Reportar cualquier anomalía al área de TI. </t>
+  </si>
+  <si>
+    <t>4. Hago constar que el equipo de cómputo es intransferible y esta estríctamente prohibido dejarlo en lugares de exposición de riesgo, daño y/o extravío.</t>
+  </si>
+  <si>
+    <t>5. Comunicar en caso de robo o extravío al área de TI.</t>
+  </si>
+  <si>
+    <t>Acepto que he comprendido claramente las responsabilidades que tengo con los equipos de trabajo que la empresa me ha otorgado y que el uso es exclusivamente laboral.</t>
+  </si>
+  <si>
+    <t>ENTREGA:</t>
+  </si>
+  <si>
+    <t>ACEPTA Y RECIBE:</t>
+  </si>
+  <si>
     <t>Supervisor Operaciones</t>
-  </si>
-  <si>
-    <t>Región:</t>
-  </si>
-  <si>
-    <t>Norte</t>
-  </si>
-  <si>
-    <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>MARCA</t>
-  </si>
-  <si>
-    <t>MODELO</t>
-  </si>
-  <si>
-    <t>NUMERO DE SERIE</t>
-  </si>
-  <si>
-    <t>OBSERVACIONES</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>wertyuiop</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>KB216T</t>
-  </si>
-  <si>
-    <t>CN-0F2JV2-LO300-0CE-00LV-A04</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>MS116T1</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-150-08Y0</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>23-08-69698</t>
-  </si>
-  <si>
-    <t>Impresora</t>
-  </si>
-  <si>
-    <t>EPSON</t>
-  </si>
-  <si>
-    <t>EconTank L6270</t>
-  </si>
-  <si>
-    <t>X8G5011801</t>
-  </si>
-  <si>
-    <t>Desktop/Monitor</t>
-  </si>
-  <si>
-    <t>Optiplex 7490 AIO</t>
-  </si>
-  <si>
-    <t>6TYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptador de Puerto  </t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>xctvgybij</t>
-  </si>
-  <si>
-    <t>DRFTGYUHJIPKO</t>
-  </si>
-  <si>
-    <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
-  </si>
-  <si>
-    <t>1. El uso correcto del equipo asignado.</t>
-  </si>
-  <si>
-    <t>2. Permitir realizar la auditoría y mantenimiento programado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Reportar cualquier anomalía al área de TI. </t>
-  </si>
-  <si>
-    <t>4. Hago constar que el equipo de cómputo es intransferible y esta estríctamente prohibido dejarlo en lugares de exposición de riesgo, daño y/o extravío.</t>
-  </si>
-  <si>
-    <t>5. Comunicar en caso de robo o extravío al área de TI.</t>
-  </si>
-  <si>
-    <t>Acepto que he comprendido claramente las responsabilidades que tengo con los equipos de trabajo que la empresa me ha otorgado y que el uso es exclusivamente laboral.</t>
-  </si>
-  <si>
-    <t>ENTREGA:</t>
-  </si>
-  <si>
-    <t>ACEPTA Y RECIBE:</t>
-  </si>
-  <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -336,6 +342,32 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -404,32 +436,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -518,41 +524,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -562,15 +538,45 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
@@ -855,7 +861,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -872,73 +878,73 @@
     <row r="1" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="2" spans="1:11" customHeight="1" ht="15.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="33" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="34"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="3" spans="1:11" customHeight="1" ht="15.75">
       <c r="A3" s="1"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="33" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:11" customHeight="1" ht="15.75">
       <c r="A4" s="1"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="33" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="34"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" customHeight="1" ht="15.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="35"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="49"/>
     </row>
     <row r="6" spans="1:11" customHeight="1" ht="9.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="36"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:11" customHeight="1" ht="15.75">
       <c r="H7" s="2"/>
@@ -950,14 +956,14 @@
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="2" t="s">
         <v>7</v>
       </c>
@@ -987,13 +993,13 @@
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="5"/>
+      <c r="I10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
       <c r="G11" s="12"/>
@@ -1003,38 +1009,38 @@
       <c r="B12" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" spans="1:11" customHeight="1" ht="15.75">
       <c r="A13" s="13"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" spans="1:11" customHeight="1" ht="15.75">
       <c r="A14" s="13"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
     </row>
     <row r="15" spans="1:11" customHeight="1" ht="15.75">
       <c r="A15" s="14"/>
@@ -1061,15 +1067,15 @@
       <c r="E16" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="34"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="34"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11">
@@ -1271,277 +1277,3025 @@
       <c r="J25" s="53"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="18"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="48"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="18"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="48"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A29" s="19"/>
-      <c r="B29" s="40" t="s">
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>9</v>
+      </c>
+      <c r="C26" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="9">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A31" s="20"/>
-      <c r="B31" s="43" t="s">
+      <c r="D26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15">
-      <c r="A32" s="20"/>
-      <c r="B32" s="43" t="s">
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15">
-      <c r="A33" s="20"/>
-      <c r="B33" s="43" t="s">
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53">
+        <v>10</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53">
+        <v>11</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53">
+        <v>12</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53">
+        <v>13</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53">
+        <v>14</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53">
+        <v>15</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="52"/>
+      <c r="B34" s="53">
+        <v>16</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53">
+        <v>17</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="52"/>
+      <c r="B36" s="53">
+        <v>18</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="52"/>
+      <c r="B37" s="53">
+        <v>19</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="52"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="52"/>
+      <c r="B39" s="53">
+        <v>20</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="52"/>
+      <c r="B40" s="53">
+        <v>21</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="52"/>
+      <c r="B41" s="53">
+        <v>22</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="52"/>
+      <c r="B42" s="53">
+        <v>23</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="52"/>
+      <c r="B43" s="53">
+        <v>24</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="52"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="52"/>
+      <c r="B45" s="53">
+        <v>25</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="52"/>
+      <c r="B46" s="53">
+        <v>26</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="52"/>
+      <c r="B47" s="53">
+        <v>27</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="52"/>
+      <c r="B48" s="53">
+        <v>28</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="52"/>
+      <c r="B49" s="53">
+        <v>29</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="52"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="52"/>
+      <c r="B51" s="53">
+        <v>30</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="52"/>
+      <c r="B52" s="53">
+        <v>31</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="52"/>
+      <c r="B53" s="53">
+        <v>32</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="52"/>
+      <c r="B54" s="53">
+        <v>33</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="52"/>
+      <c r="B55" s="53">
+        <v>34</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="52"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="52"/>
+      <c r="B57" s="53">
+        <v>35</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="52"/>
+      <c r="B58" s="53">
+        <v>36</v>
+      </c>
+      <c r="C58" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="52"/>
+      <c r="B59" s="53">
+        <v>37</v>
+      </c>
+      <c r="C59" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="52"/>
+      <c r="B60" s="53">
+        <v>38</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="52"/>
+      <c r="B61" s="53">
+        <v>39</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="17"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="52"/>
+      <c r="B62" s="53"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="17"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="52"/>
+      <c r="B63" s="53">
+        <v>40</v>
+      </c>
+      <c r="C63" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="53"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="53"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="52"/>
+      <c r="B64" s="53">
+        <v>41</v>
+      </c>
+      <c r="C64" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="52"/>
+      <c r="B65" s="53">
+        <v>42</v>
+      </c>
+      <c r="C65" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="52"/>
+      <c r="B66" s="53">
+        <v>43</v>
+      </c>
+      <c r="C66" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E66" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="52"/>
+      <c r="B67" s="53">
+        <v>44</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="53"/>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="52"/>
+      <c r="B68" s="53"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="52"/>
+      <c r="B69" s="53">
+        <v>45</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="53"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="52"/>
+      <c r="B70" s="53">
+        <v>46</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H70" s="53"/>
+      <c r="I70" s="53"/>
+      <c r="J70" s="53"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="52"/>
+      <c r="B71" s="53">
+        <v>47</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E71" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" s="53"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="53"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="52"/>
+      <c r="B72" s="53">
+        <v>48</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="53"/>
+      <c r="K72" s="17"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="52"/>
+      <c r="B73" s="53">
+        <v>49</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D73" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="52"/>
+      <c r="B74" s="53"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="52"/>
+      <c r="B75" s="53">
         <v>50</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15">
-      <c r="A34" s="20"/>
-      <c r="B34" s="43" t="s">
+      <c r="C75" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="53"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="52"/>
+      <c r="B76" s="53">
         <v>51</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15">
-      <c r="A35" s="20"/>
-      <c r="B35" s="43" t="s">
+      <c r="C76" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="52"/>
+      <c r="B77" s="53">
         <v>52</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-    </row>
-    <row r="36" spans="1:11" customHeight="1" ht="12">
-      <c r="A36" s="21"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A37" s="17"/>
-      <c r="B37" s="45" t="s">
+      <c r="C77" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E77" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" s="53"/>
+      <c r="I77" s="53"/>
+      <c r="J77" s="53"/>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="52"/>
+      <c r="B78" s="53">
         <v>53</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="41" t="s">
+      <c r="C78" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E78" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
+      <c r="J78" s="53"/>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="52"/>
+      <c r="B79" s="53">
         <v>54</v>
       </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="H40" s="42" t="s">
+      <c r="C79" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="53"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="52"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
+      <c r="J80" s="53"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="52"/>
+      <c r="B81" s="53">
         <v>55</v>
       </c>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-    </row>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C44" s="41" t="s">
+      <c r="C81" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="53"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="53"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="52"/>
+      <c r="B82" s="53">
         <v>56</v>
       </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="H44" s="41" t="str">
+      <c r="C82" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H82" s="53"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="53"/>
+      <c r="K82" s="17"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="52"/>
+      <c r="B83" s="53">
+        <v>57</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E83" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" s="53"/>
+      <c r="I83" s="53"/>
+      <c r="J83" s="53"/>
+      <c r="K83" s="17"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="52"/>
+      <c r="B84" s="53">
+        <v>58</v>
+      </c>
+      <c r="C84" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H84" s="53"/>
+      <c r="I84" s="53"/>
+      <c r="J84" s="53"/>
+      <c r="K84" s="17"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="52"/>
+      <c r="B85" s="53">
+        <v>59</v>
+      </c>
+      <c r="C85" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D85" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H85" s="53"/>
+      <c r="I85" s="53"/>
+      <c r="J85" s="53"/>
+      <c r="K85" s="17"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="52"/>
+      <c r="B86" s="53"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
+      <c r="I86" s="53"/>
+      <c r="J86" s="53"/>
+      <c r="K86" s="17"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="52"/>
+      <c r="B87" s="53">
+        <v>60</v>
+      </c>
+      <c r="C87" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="17"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="52"/>
+      <c r="B88" s="53">
+        <v>61</v>
+      </c>
+      <c r="C88" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="17"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="52"/>
+      <c r="B89" s="53">
+        <v>62</v>
+      </c>
+      <c r="C89" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D89" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" s="53"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="52"/>
+      <c r="B90" s="53">
+        <v>63</v>
+      </c>
+      <c r="C90" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D90" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H90" s="53"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="52"/>
+      <c r="B91" s="53">
+        <v>64</v>
+      </c>
+      <c r="C91" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H91" s="53"/>
+      <c r="I91" s="53"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="17"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="52"/>
+      <c r="B92" s="53"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
+      <c r="E92" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53"/>
+      <c r="H92" s="53"/>
+      <c r="I92" s="53"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="52"/>
+      <c r="B93" s="53">
+        <v>65</v>
+      </c>
+      <c r="C93" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="53"/>
+      <c r="I93" s="53"/>
+      <c r="J93" s="53"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="52"/>
+      <c r="B94" s="53">
+        <v>66</v>
+      </c>
+      <c r="C94" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H94" s="53"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="17"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="52"/>
+      <c r="B95" s="53">
+        <v>67</v>
+      </c>
+      <c r="C95" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="53"/>
+      <c r="G95" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" s="53"/>
+      <c r="I95" s="53"/>
+      <c r="J95" s="53"/>
+      <c r="K95" s="17"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="52"/>
+      <c r="B96" s="53">
+        <v>68</v>
+      </c>
+      <c r="C96" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E96" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H96" s="53"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="17"/>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="52"/>
+      <c r="B97" s="53">
+        <v>69</v>
+      </c>
+      <c r="C97" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D97" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F97" s="53"/>
+      <c r="G97" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H97" s="53"/>
+      <c r="I97" s="53"/>
+      <c r="J97" s="53"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="52"/>
+      <c r="B98" s="53"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="53"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="52"/>
+      <c r="B99" s="53">
+        <v>70</v>
+      </c>
+      <c r="C99" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E99" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F99" s="53"/>
+      <c r="G99" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H99" s="53"/>
+      <c r="I99" s="53"/>
+      <c r="J99" s="53"/>
+      <c r="K99" s="17"/>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="52"/>
+      <c r="B100" s="53">
+        <v>71</v>
+      </c>
+      <c r="C100" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H100" s="53"/>
+      <c r="I100" s="53"/>
+      <c r="J100" s="53"/>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="52"/>
+      <c r="B101" s="53">
+        <v>72</v>
+      </c>
+      <c r="C101" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D101" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F101" s="53"/>
+      <c r="G101" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H101" s="53"/>
+      <c r="I101" s="53"/>
+      <c r="J101" s="53"/>
+      <c r="K101" s="17"/>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="52"/>
+      <c r="B102" s="53">
+        <v>73</v>
+      </c>
+      <c r="C102" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H102" s="53"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="17"/>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="52"/>
+      <c r="B103" s="53">
+        <v>74</v>
+      </c>
+      <c r="C103" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D103" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H103" s="53"/>
+      <c r="I103" s="53"/>
+      <c r="J103" s="53"/>
+      <c r="K103" s="17"/>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="52"/>
+      <c r="B104" s="53"/>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
+      <c r="I104" s="53"/>
+      <c r="J104" s="53"/>
+      <c r="K104" s="17"/>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="52"/>
+      <c r="B105" s="53">
+        <v>75</v>
+      </c>
+      <c r="C105" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E105" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H105" s="53"/>
+      <c r="I105" s="53"/>
+      <c r="J105" s="53"/>
+      <c r="K105" s="17"/>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="52"/>
+      <c r="B106" s="53">
+        <v>76</v>
+      </c>
+      <c r="C106" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D106" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H106" s="53"/>
+      <c r="I106" s="53"/>
+      <c r="J106" s="53"/>
+      <c r="K106" s="17"/>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="52"/>
+      <c r="B107" s="53">
+        <v>77</v>
+      </c>
+      <c r="C107" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D107" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E107" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" s="53"/>
+      <c r="G107" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" s="53"/>
+      <c r="I107" s="53"/>
+      <c r="J107" s="53"/>
+      <c r="K107" s="17"/>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="52"/>
+      <c r="B108" s="53">
+        <v>78</v>
+      </c>
+      <c r="C108" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D108" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108" s="53"/>
+      <c r="G108" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H108" s="53"/>
+      <c r="I108" s="53"/>
+      <c r="J108" s="53"/>
+      <c r="K108" s="17"/>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="52"/>
+      <c r="B109" s="53">
+        <v>79</v>
+      </c>
+      <c r="C109" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D109" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H109" s="53"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="17"/>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="52"/>
+      <c r="B110" s="53"/>
+      <c r="C110" s="53"/>
+      <c r="D110" s="53"/>
+      <c r="E110" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F110" s="53"/>
+      <c r="G110" s="53"/>
+      <c r="H110" s="53"/>
+      <c r="I110" s="53"/>
+      <c r="J110" s="53"/>
+      <c r="K110" s="17"/>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="52"/>
+      <c r="B111" s="53">
+        <v>80</v>
+      </c>
+      <c r="C111" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E111" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F111" s="53"/>
+      <c r="G111" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="53"/>
+      <c r="I111" s="53"/>
+      <c r="J111" s="53"/>
+      <c r="K111" s="17"/>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="52"/>
+      <c r="B112" s="53">
+        <v>81</v>
+      </c>
+      <c r="C112" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D112" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E112" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" s="53"/>
+      <c r="G112" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H112" s="53"/>
+      <c r="I112" s="53"/>
+      <c r="J112" s="53"/>
+      <c r="K112" s="17"/>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" s="52"/>
+      <c r="B113" s="53">
+        <v>82</v>
+      </c>
+      <c r="C113" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E113" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="53"/>
+      <c r="G113" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H113" s="53"/>
+      <c r="I113" s="53"/>
+      <c r="J113" s="53"/>
+      <c r="K113" s="17"/>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" s="52"/>
+      <c r="B114" s="53">
+        <v>83</v>
+      </c>
+      <c r="C114" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D114" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" s="53"/>
+      <c r="G114" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H114" s="53"/>
+      <c r="I114" s="53"/>
+      <c r="J114" s="53"/>
+      <c r="K114" s="17"/>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" s="52"/>
+      <c r="B115" s="53">
+        <v>84</v>
+      </c>
+      <c r="C115" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D115" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E115" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F115" s="53"/>
+      <c r="G115" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H115" s="53"/>
+      <c r="I115" s="53"/>
+      <c r="J115" s="53"/>
+      <c r="K115" s="17"/>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" s="52"/>
+      <c r="B116" s="53"/>
+      <c r="C116" s="53"/>
+      <c r="D116" s="53"/>
+      <c r="E116" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="53"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="53"/>
+      <c r="I116" s="53"/>
+      <c r="J116" s="53"/>
+      <c r="K116" s="17"/>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="52"/>
+      <c r="B117" s="53">
+        <v>85</v>
+      </c>
+      <c r="C117" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D117" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E117" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F117" s="53"/>
+      <c r="G117" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="53"/>
+      <c r="I117" s="53"/>
+      <c r="J117" s="53"/>
+      <c r="K117" s="17"/>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" s="52"/>
+      <c r="B118" s="53">
+        <v>86</v>
+      </c>
+      <c r="C118" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D118" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E118" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F118" s="53"/>
+      <c r="G118" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H118" s="53"/>
+      <c r="I118" s="53"/>
+      <c r="J118" s="53"/>
+      <c r="K118" s="17"/>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="52"/>
+      <c r="B119" s="53">
+        <v>87</v>
+      </c>
+      <c r="C119" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D119" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E119" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F119" s="53"/>
+      <c r="G119" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H119" s="53"/>
+      <c r="I119" s="53"/>
+      <c r="J119" s="53"/>
+      <c r="K119" s="17"/>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" s="52"/>
+      <c r="B120" s="53">
+        <v>88</v>
+      </c>
+      <c r="C120" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D120" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E120" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F120" s="53"/>
+      <c r="G120" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H120" s="53"/>
+      <c r="I120" s="53"/>
+      <c r="J120" s="53"/>
+      <c r="K120" s="17"/>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" s="52"/>
+      <c r="B121" s="53">
+        <v>89</v>
+      </c>
+      <c r="C121" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D121" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E121" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F121" s="53"/>
+      <c r="G121" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H121" s="53"/>
+      <c r="I121" s="53"/>
+      <c r="J121" s="53"/>
+      <c r="K121" s="17"/>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" s="52"/>
+      <c r="B122" s="53"/>
+      <c r="C122" s="53"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" s="53"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="53"/>
+      <c r="I122" s="53"/>
+      <c r="J122" s="53"/>
+      <c r="K122" s="17"/>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" s="52"/>
+      <c r="B123" s="53">
+        <v>90</v>
+      </c>
+      <c r="C123" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E123" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F123" s="53"/>
+      <c r="G123" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" s="53"/>
+      <c r="I123" s="53"/>
+      <c r="J123" s="53"/>
+      <c r="K123" s="17"/>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" s="52"/>
+      <c r="B124" s="53">
+        <v>91</v>
+      </c>
+      <c r="C124" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E124" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F124" s="53"/>
+      <c r="G124" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H124" s="53"/>
+      <c r="I124" s="53"/>
+      <c r="J124" s="53"/>
+      <c r="K124" s="17"/>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" s="52"/>
+      <c r="B125" s="53">
+        <v>92</v>
+      </c>
+      <c r="C125" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D125" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E125" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F125" s="53"/>
+      <c r="G125" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H125" s="53"/>
+      <c r="I125" s="53"/>
+      <c r="J125" s="53"/>
+      <c r="K125" s="17"/>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" s="52"/>
+      <c r="B126" s="53">
+        <v>93</v>
+      </c>
+      <c r="C126" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D126" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E126" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F126" s="53"/>
+      <c r="G126" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H126" s="53"/>
+      <c r="I126" s="53"/>
+      <c r="J126" s="53"/>
+      <c r="K126" s="17"/>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" s="52"/>
+      <c r="B127" s="53">
+        <v>94</v>
+      </c>
+      <c r="C127" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D127" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E127" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F127" s="53"/>
+      <c r="G127" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H127" s="53"/>
+      <c r="I127" s="53"/>
+      <c r="J127" s="53"/>
+      <c r="K127" s="17"/>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" s="52"/>
+      <c r="B128" s="53"/>
+      <c r="C128" s="53"/>
+      <c r="D128" s="53"/>
+      <c r="E128" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128" s="53"/>
+      <c r="G128" s="53"/>
+      <c r="H128" s="53"/>
+      <c r="I128" s="53"/>
+      <c r="J128" s="53"/>
+      <c r="K128" s="17"/>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" s="52"/>
+      <c r="B129" s="53">
+        <v>95</v>
+      </c>
+      <c r="C129" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D129" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E129" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F129" s="53"/>
+      <c r="G129" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H129" s="53"/>
+      <c r="I129" s="53"/>
+      <c r="J129" s="53"/>
+      <c r="K129" s="17"/>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="52"/>
+      <c r="B130" s="53">
+        <v>96</v>
+      </c>
+      <c r="C130" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D130" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E130" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130" s="53"/>
+      <c r="G130" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H130" s="53"/>
+      <c r="I130" s="53"/>
+      <c r="J130" s="53"/>
+      <c r="K130" s="17"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="52"/>
+      <c r="B131" s="53">
+        <v>97</v>
+      </c>
+      <c r="C131" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D131" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E131" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" s="53"/>
+      <c r="G131" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H131" s="53"/>
+      <c r="I131" s="53"/>
+      <c r="J131" s="53"/>
+      <c r="K131" s="17"/>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="52"/>
+      <c r="B132" s="53">
+        <v>98</v>
+      </c>
+      <c r="C132" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D132" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E132" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F132" s="53"/>
+      <c r="G132" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H132" s="53"/>
+      <c r="I132" s="53"/>
+      <c r="J132" s="53"/>
+      <c r="K132" s="17"/>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="52"/>
+      <c r="B133" s="53">
+        <v>99</v>
+      </c>
+      <c r="C133" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D133" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E133" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F133" s="53"/>
+      <c r="G133" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H133" s="53"/>
+      <c r="I133" s="53"/>
+      <c r="J133" s="53"/>
+      <c r="K133" s="17"/>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" s="52"/>
+      <c r="B134" s="53"/>
+      <c r="C134" s="53"/>
+      <c r="D134" s="53"/>
+      <c r="E134" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F134" s="53"/>
+      <c r="G134" s="53"/>
+      <c r="H134" s="53"/>
+      <c r="I134" s="53"/>
+      <c r="J134" s="53"/>
+      <c r="K134" s="17"/>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" s="52"/>
+      <c r="B135" s="53">
+        <v>100</v>
+      </c>
+      <c r="C135" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D135" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E135" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F135" s="53"/>
+      <c r="G135" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H135" s="53"/>
+      <c r="I135" s="53"/>
+      <c r="J135" s="53"/>
+      <c r="K135" s="17"/>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" s="52"/>
+      <c r="B136" s="53">
+        <v>101</v>
+      </c>
+      <c r="C136" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D136" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E136" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="53"/>
+      <c r="G136" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H136" s="53"/>
+      <c r="I136" s="53"/>
+      <c r="J136" s="53"/>
+      <c r="K136" s="17"/>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" s="52"/>
+      <c r="B137" s="53">
+        <v>102</v>
+      </c>
+      <c r="C137" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D137" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E137" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F137" s="53"/>
+      <c r="G137" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H137" s="53"/>
+      <c r="I137" s="53"/>
+      <c r="J137" s="53"/>
+      <c r="K137" s="17"/>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" s="52"/>
+      <c r="B138" s="53">
+        <v>103</v>
+      </c>
+      <c r="C138" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D138" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E138" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F138" s="53"/>
+      <c r="G138" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H138" s="53"/>
+      <c r="I138" s="53"/>
+      <c r="J138" s="53"/>
+      <c r="K138" s="17"/>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" s="52"/>
+      <c r="B139" s="53">
+        <v>104</v>
+      </c>
+      <c r="C139" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D139" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E139" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F139" s="53"/>
+      <c r="G139" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H139" s="53"/>
+      <c r="I139" s="53"/>
+      <c r="J139" s="53"/>
+      <c r="K139" s="17"/>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" s="52"/>
+      <c r="B140" s="53"/>
+      <c r="C140" s="53"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F140" s="53"/>
+      <c r="G140" s="53"/>
+      <c r="H140" s="53"/>
+      <c r="I140" s="53"/>
+      <c r="J140" s="53"/>
+      <c r="K140" s="17"/>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" s="52"/>
+      <c r="B141" s="53">
+        <v>105</v>
+      </c>
+      <c r="C141" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D141" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E141" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F141" s="53"/>
+      <c r="G141" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H141" s="53"/>
+      <c r="I141" s="53"/>
+      <c r="J141" s="53"/>
+      <c r="K141" s="17"/>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" s="52"/>
+      <c r="B142" s="53">
+        <v>106</v>
+      </c>
+      <c r="C142" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D142" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E142" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142" s="53"/>
+      <c r="G142" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H142" s="53"/>
+      <c r="I142" s="53"/>
+      <c r="J142" s="53"/>
+      <c r="K142" s="17"/>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" s="52"/>
+      <c r="B143" s="53">
+        <v>107</v>
+      </c>
+      <c r="C143" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D143" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E143" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F143" s="53"/>
+      <c r="G143" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H143" s="53"/>
+      <c r="I143" s="53"/>
+      <c r="J143" s="53"/>
+      <c r="K143" s="17"/>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" s="52"/>
+      <c r="B144" s="53">
+        <v>108</v>
+      </c>
+      <c r="C144" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D144" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E144" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F144" s="53"/>
+      <c r="G144" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H144" s="53"/>
+      <c r="I144" s="53"/>
+      <c r="J144" s="53"/>
+      <c r="K144" s="17"/>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" s="52"/>
+      <c r="B145" s="53">
+        <v>109</v>
+      </c>
+      <c r="C145" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D145" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E145" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F145" s="53"/>
+      <c r="G145" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H145" s="53"/>
+      <c r="I145" s="53"/>
+      <c r="J145" s="53"/>
+      <c r="K145" s="17"/>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" s="52"/>
+      <c r="B146" s="53"/>
+      <c r="C146" s="53"/>
+      <c r="D146" s="53"/>
+      <c r="E146" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146" s="53"/>
+      <c r="G146" s="53"/>
+      <c r="H146" s="53"/>
+      <c r="I146" s="53"/>
+      <c r="J146" s="53"/>
+      <c r="K146" s="17"/>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" s="52"/>
+      <c r="B147" s="53">
+        <v>110</v>
+      </c>
+      <c r="C147" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E147" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F147" s="53"/>
+      <c r="G147" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H147" s="53"/>
+      <c r="I147" s="53"/>
+      <c r="J147" s="53"/>
+      <c r="K147" s="17"/>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" s="52"/>
+      <c r="B148" s="53">
+        <v>111</v>
+      </c>
+      <c r="C148" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D148" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E148" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148" s="53"/>
+      <c r="G148" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148" s="53"/>
+      <c r="I148" s="53"/>
+      <c r="J148" s="53"/>
+      <c r="K148" s="17"/>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" s="52"/>
+      <c r="B149" s="53">
+        <v>112</v>
+      </c>
+      <c r="C149" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D149" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E149" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F149" s="53"/>
+      <c r="G149" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H149" s="53"/>
+      <c r="I149" s="53"/>
+      <c r="J149" s="53"/>
+      <c r="K149" s="17"/>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" s="52"/>
+      <c r="B150" s="53">
+        <v>113</v>
+      </c>
+      <c r="C150" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D150" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E150" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F150" s="53"/>
+      <c r="G150" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H150" s="53"/>
+      <c r="I150" s="53"/>
+      <c r="J150" s="53"/>
+      <c r="K150" s="17"/>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" s="52"/>
+      <c r="B151" s="53">
+        <v>114</v>
+      </c>
+      <c r="C151" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D151" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E151" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F151" s="53"/>
+      <c r="G151" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H151" s="53"/>
+      <c r="I151" s="53"/>
+      <c r="J151" s="53"/>
+      <c r="K151" s="17"/>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" s="52"/>
+      <c r="B152" s="53"/>
+      <c r="C152" s="53"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="53"/>
+      <c r="G152" s="53"/>
+      <c r="H152" s="53"/>
+      <c r="I152" s="53"/>
+      <c r="J152" s="53"/>
+      <c r="K152" s="17"/>
+    </row>
+    <row r="153" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A153" s="18"/>
+      <c r="B153" s="24"/>
+      <c r="C153" s="24"/>
+      <c r="D153" s="24"/>
+      <c r="E153" s="35"/>
+      <c r="F153" s="31"/>
+      <c r="G153" s="35"/>
+      <c r="H153" s="31"/>
+      <c r="I153" s="35"/>
+      <c r="J153" s="31"/>
+    </row>
+    <row r="154" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A154" s="18"/>
+      <c r="B154" s="24"/>
+      <c r="C154" s="24"/>
+      <c r="D154" s="24"/>
+      <c r="E154" s="30"/>
+      <c r="F154" s="31"/>
+      <c r="G154" s="32"/>
+      <c r="H154" s="31"/>
+      <c r="I154" s="32"/>
+      <c r="J154" s="31"/>
+    </row>
+    <row r="155" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A155" s="13"/>
+      <c r="B155" s="13"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="I155" s="13"/>
+      <c r="J155" s="13"/>
+    </row>
+    <row r="156" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A156" s="19"/>
+      <c r="B156" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C156" s="26"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="26"/>
+      <c r="F156" s="26"/>
+      <c r="G156" s="26"/>
+      <c r="H156" s="26"/>
+      <c r="I156" s="26"/>
+      <c r="J156" s="26"/>
+    </row>
+    <row r="157" spans="1:11" customHeight="1" ht="9">
+      <c r="A157" s="20"/>
+      <c r="B157" s="20"/>
+      <c r="C157" s="20"/>
+      <c r="D157" s="20"/>
+      <c r="E157" s="20"/>
+      <c r="F157" s="20"/>
+      <c r="G157" s="20"/>
+      <c r="H157" s="20"/>
+      <c r="I157" s="20"/>
+      <c r="J157" s="20"/>
+    </row>
+    <row r="158" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A158" s="20"/>
+      <c r="B158" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C158" s="26"/>
+      <c r="D158" s="26"/>
+      <c r="E158" s="26"/>
+      <c r="F158" s="26"/>
+      <c r="G158" s="26"/>
+      <c r="H158" s="26"/>
+      <c r="I158" s="26"/>
+      <c r="J158" s="26"/>
+    </row>
+    <row r="159" spans="1:11" customHeight="1" ht="15">
+      <c r="A159" s="20"/>
+      <c r="B159" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C159" s="26"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="26"/>
+      <c r="F159" s="26"/>
+      <c r="G159" s="26"/>
+      <c r="H159" s="26"/>
+      <c r="I159" s="26"/>
+      <c r="J159" s="26"/>
+    </row>
+    <row r="160" spans="1:11" customHeight="1" ht="15">
+      <c r="A160" s="20"/>
+      <c r="B160" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C160" s="26"/>
+      <c r="D160" s="26"/>
+      <c r="E160" s="26"/>
+      <c r="F160" s="26"/>
+      <c r="G160" s="26"/>
+      <c r="H160" s="26"/>
+      <c r="I160" s="26"/>
+      <c r="J160" s="26"/>
+    </row>
+    <row r="161" spans="1:11" customHeight="1" ht="15">
+      <c r="A161" s="20"/>
+      <c r="B161" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C161" s="26"/>
+      <c r="D161" s="26"/>
+      <c r="E161" s="26"/>
+      <c r="F161" s="26"/>
+      <c r="G161" s="26"/>
+      <c r="H161" s="26"/>
+      <c r="I161" s="26"/>
+      <c r="J161" s="26"/>
+    </row>
+    <row r="162" spans="1:11" customHeight="1" ht="15">
+      <c r="A162" s="20"/>
+      <c r="B162" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C162" s="26"/>
+      <c r="D162" s="26"/>
+      <c r="E162" s="26"/>
+      <c r="F162" s="26"/>
+      <c r="G162" s="26"/>
+      <c r="H162" s="26"/>
+      <c r="I162" s="26"/>
+      <c r="J162" s="26"/>
+    </row>
+    <row r="163" spans="1:11" customHeight="1" ht="12">
+      <c r="A163" s="21"/>
+      <c r="B163" s="28"/>
+      <c r="C163" s="26"/>
+      <c r="D163" s="26"/>
+      <c r="E163" s="26"/>
+      <c r="F163" s="26"/>
+      <c r="G163" s="26"/>
+      <c r="H163" s="26"/>
+      <c r="I163" s="26"/>
+      <c r="J163" s="26"/>
+    </row>
+    <row r="164" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A164" s="17"/>
+      <c r="B164" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C164" s="26"/>
+      <c r="D164" s="26"/>
+      <c r="E164" s="26"/>
+      <c r="F164" s="26"/>
+      <c r="G164" s="26"/>
+      <c r="H164" s="26"/>
+      <c r="I164" s="26"/>
+      <c r="J164" s="26"/>
+    </row>
+    <row r="165" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A165" s="22"/>
+      <c r="B165" s="22"/>
+      <c r="C165" s="22"/>
+      <c r="D165" s="22"/>
+      <c r="E165" s="22"/>
+      <c r="H165" s="15"/>
+      <c r="I165" s="15"/>
+      <c r="J165" s="15"/>
+    </row>
+    <row r="166" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C166" s="22"/>
+      <c r="D166" s="22"/>
+      <c r="E166" s="22"/>
+      <c r="I166" s="15"/>
+      <c r="J166" s="15"/>
+    </row>
+    <row r="167" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A167" s="22"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="H167" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I167" s="26"/>
+      <c r="J167" s="26"/>
+    </row>
+    <row r="168" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="169" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C169" s="23"/>
+      <c r="D169" s="23"/>
+      <c r="E169" s="23"/>
+      <c r="H169" s="23"/>
+      <c r="I169" s="23"/>
+      <c r="J169" s="23"/>
+    </row>
+    <row r="170" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="171" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C171" s="25"/>
+      <c r="D171" s="26"/>
+      <c r="E171" s="26"/>
+      <c r="H171" s="25" t="str">
         <f>C8</f>
         <v>Alan Bauza Valdez</v>
       </c>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-    </row>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C45" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="H45" s="41" t="str">
-        <f>C10</f>
-        <v>Supervisor Operaciones</v>
-      </c>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-    </row>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-    </row>
-    <row r="47" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="48" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
+      <c r="I171" s="26"/>
+      <c r="J171" s="26"/>
+    </row>
+    <row r="172" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C172" s="25"/>
+      <c r="D172" s="26"/>
+      <c r="E172" s="26"/>
+      <c r="H172" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I172" s="26"/>
+      <c r="J172" s="26"/>
+    </row>
+    <row r="173" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H173" s="22"/>
+      <c r="I173" s="22"/>
+      <c r="J173" s="22"/>
+    </row>
+    <row r="174" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="175" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A175" s="22"/>
+      <c r="B175" s="22"/>
+      <c r="C175" s="22"/>
+      <c r="D175" s="22"/>
+      <c r="E175" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="B12:J14"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:H4"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C5:J6"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B12:J14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="I153:J153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="B156:J156"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="H167:J167"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="H171:J171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="H172:J172"/>
+    <mergeCell ref="B158:J158"/>
+    <mergeCell ref="B159:J159"/>
+    <mergeCell ref="B160:J160"/>
+    <mergeCell ref="B161:J161"/>
+    <mergeCell ref="B162:J162"/>
+    <mergeCell ref="B163:J163"/>
+    <mergeCell ref="B164:J164"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1569,7 +4323,388 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I17:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="I104:J104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="I106:J106"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="I109:J109"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="I110:J110"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="G118:H118"/>
+    <mergeCell ref="I118:J118"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="I119:J119"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="I120:J120"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="I121:J121"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="I122:J122"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="G123:H123"/>
+    <mergeCell ref="I123:J123"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="G124:H124"/>
+    <mergeCell ref="I124:J124"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="G130:H130"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="G131:H131"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="G132:H132"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="G134:H134"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="I139:J139"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="I140:J140"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="I141:J141"/>
+    <mergeCell ref="E142:F142"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="I142:J142"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="I143:J143"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="I144:J144"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="E146:F146"/>
+    <mergeCell ref="G146:H146"/>
+    <mergeCell ref="I146:J146"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="G147:H147"/>
+    <mergeCell ref="I147:J147"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="G148:H148"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="G149:H149"/>
+    <mergeCell ref="I149:J149"/>
+    <mergeCell ref="E150:F150"/>
+    <mergeCell ref="G150:H150"/>
+    <mergeCell ref="I150:J150"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="I151:J151"/>
+    <mergeCell ref="E152:F152"/>
+    <mergeCell ref="G152:H152"/>
+    <mergeCell ref="I152:J152"/>
+    <mergeCell ref="I17:J152"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,25 +41,25 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>02/07/2025</t>
+    <t>07/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>yfuyf</t>
   </si>
   <si>
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>Base Operativa</t>
+    <t>giygilug</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -95,13 +95,16 @@
     <t>1446MG00C698</t>
   </si>
   <si>
+    <t>cyufcyivb</t>
+  </si>
+  <si>
     <t>Y8GS78BY8</t>
   </si>
   <si>
     <t>Cargador de Laptop</t>
   </si>
   <si>
-    <t>Tesla</t>
+    <t>HP</t>
   </si>
   <si>
     <t>LA65NM190</t>
@@ -191,10 +194,10 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Darwin Ruiz Aguilar</t>
+  </si>
+  <si>
+    <t>Coordinador de Mantenimiento</t>
   </si>
   <si>
     <t>Supervisor Operaciones</t>
@@ -1102,7 +1105,9 @@
         <v>25</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
+      <c r="I17" s="53" t="s">
+        <v>26</v>
+      </c>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
@@ -1112,7 +1117,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1127,17 +1132,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1150,17 +1155,17 @@
         <v>3</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
@@ -1173,17 +1178,17 @@
         <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1196,17 +1201,17 @@
         <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1219,17 +1224,17 @@
         <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1242,17 +1247,17 @@
         <v>7</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
@@ -1265,7 +1270,7 @@
       <c r="C25" s="53"/>
       <c r="D25" s="53"/>
       <c r="E25" s="51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="53"/>
@@ -1313,7 +1318,7 @@
     <row r="29" spans="1:11" customHeight="1" ht="15.75">
       <c r="A29" s="19"/>
       <c r="B29" s="33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1339,7 +1344,7 @@
     <row r="31" spans="1:11" customHeight="1" ht="15.75">
       <c r="A31" s="20"/>
       <c r="B31" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1353,7 +1358,7 @@
     <row r="32" spans="1:11" customHeight="1" ht="15">
       <c r="A32" s="20"/>
       <c r="B32" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1367,7 +1372,7 @@
     <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
       <c r="B33" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
@@ -1381,7 +1386,7 @@
     <row r="34" spans="1:11" customHeight="1" ht="15">
       <c r="A34" s="20"/>
       <c r="B34" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -1395,7 +1400,7 @@
     <row r="35" spans="1:11" customHeight="1" ht="15">
       <c r="A35" s="20"/>
       <c r="B35" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -1421,7 +1426,7 @@
     <row r="37" spans="1:11" customHeight="1" ht="27.75">
       <c r="A37" s="17"/>
       <c r="B37" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -1453,12 +1458,12 @@
       <c r="A40" s="22"/>
       <c r="B40" s="22"/>
       <c r="C40" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="26"/>
       <c r="H40" s="34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="26"/>
@@ -1475,7 +1480,7 @@
     <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="44" spans="1:11" customHeight="1" ht="15.75">
       <c r="C44" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D44" s="26"/>
       <c r="E44" s="26"/>
@@ -1488,12 +1493,12 @@
     </row>
     <row r="45" spans="1:11" customHeight="1" ht="15.75">
       <c r="C45" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="26"/>
       <c r="H45" s="25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I45" s="26"/>
       <c r="J45" s="26"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,25 +41,25 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>07/07/2025</t>
+    <t>14/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>yfuyf</t>
+    <t>TI</t>
   </si>
   <si>
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>giygilug</t>
+    <t>SUR</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -95,9 +95,6 @@
     <t>1446MG00C698</t>
   </si>
   <si>
-    <t>cyufcyivb</t>
-  </si>
-  <si>
     <t>Y8GS78BY8</t>
   </si>
   <si>
@@ -116,6 +113,21 @@
     <t>Teclado</t>
   </si>
   <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG0C698O</t>
+  </si>
+  <si>
+    <t>MK235</t>
+  </si>
+  <si>
+    <t>2134MR38A788</t>
+  </si>
+  <si>
     <t>KB216T</t>
   </si>
   <si>
@@ -143,30 +155,6 @@
     <t>23-08-69698</t>
   </si>
   <si>
-    <t>Impresora</t>
-  </si>
-  <si>
-    <t>EPSON</t>
-  </si>
-  <si>
-    <t>EconTank L6270</t>
-  </si>
-  <si>
-    <t>X8G5011801</t>
-  </si>
-  <si>
-    <t>Desktop/Monitor</t>
-  </si>
-  <si>
-    <t>Optiplex 7490 AIO</t>
-  </si>
-  <si>
-    <t>6TYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00098</t>
-  </si>
-  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -194,10 +182,10 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Darwin Ruiz Aguilar</t>
-  </si>
-  <si>
-    <t>Coordinador de Mantenimiento</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
   <si>
     <t>Supervisor Operaciones</t>
@@ -867,7 +855,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1105,9 +1093,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53" t="s">
-        <v>26</v>
-      </c>
+      <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
@@ -1117,7 +1103,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1132,17 +1118,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="E19" s="53" t="s">
         <v>29</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>30</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1155,10 +1141,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="53" t="s">
         <v>32</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>23</v>
       </c>
       <c r="E20" s="53" t="s">
         <v>33</v>
@@ -1178,17 +1164,17 @@
         <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>35</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>36</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1201,17 +1187,17 @@
         <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1224,17 +1210,17 @@
         <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1247,104 +1233,103 @@
         <v>7</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
       <c r="J24" s="53"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="52"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="17"/>
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A25" s="18"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="31"/>
     </row>
     <row r="26" spans="1:11" customHeight="1" ht="15.75">
       <c r="A26" s="18"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="35"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="31"/>
-      <c r="G26" s="35"/>
+      <c r="G26" s="32"/>
       <c r="H26" s="31"/>
-      <c r="I26" s="35"/>
+      <c r="I26" s="32"/>
       <c r="J26" s="31"/>
     </row>
     <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="18"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="31"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A29" s="19"/>
-      <c r="B29" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="9">
+      <c r="A28" s="19"/>
+      <c r="B28" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="9">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:11" customHeight="1" ht="15.75">
       <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
+      <c r="B30" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15">
       <c r="A31" s="20"/>
       <c r="B31" s="27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1358,7 +1343,7 @@
     <row r="32" spans="1:11" customHeight="1" ht="15">
       <c r="A32" s="20"/>
       <c r="B32" s="27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1372,7 +1357,7 @@
     <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
       <c r="B33" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
@@ -1386,7 +1371,7 @@
     <row r="34" spans="1:11" customHeight="1" ht="15">
       <c r="A34" s="20"/>
       <c r="B34" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -1397,11 +1382,9 @@
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15">
-      <c r="A35" s="20"/>
-      <c r="B35" s="27" t="s">
-        <v>55</v>
-      </c>
+    <row r="35" spans="1:11" customHeight="1" ht="12">
+      <c r="A35" s="21"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -1411,9 +1394,11 @@
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:11" customHeight="1" ht="12">
-      <c r="A36" s="21"/>
-      <c r="B36" s="28"/>
+    <row r="36" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A36" s="17"/>
+      <c r="B36" s="29" t="s">
+        <v>52</v>
+      </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
@@ -1423,98 +1408,84 @@
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A37" s="17"/>
-      <c r="B37" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
-      <c r="H38" s="15"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="H40" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-    </row>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="H39" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+    </row>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C43" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="H43" s="25" t="str">
+        <f>C8</f>
+        <v>Alan Bauza Valdez</v>
+      </c>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+    </row>
     <row r="44" spans="1:11" customHeight="1" ht="15.75">
       <c r="C44" s="25" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D44" s="26"/>
       <c r="E44" s="26"/>
-      <c r="H44" s="25" t="str">
-        <f>C8</f>
-        <v>Alan Bauza Valdez</v>
+      <c r="H44" s="25" t="s">
+        <v>57</v>
       </c>
       <c r="I44" s="26"/>
       <c r="J44" s="26"/>
     </row>
     <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C45" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="H45" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-    </row>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-    </row>
-    <row r="47" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="48" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+    </row>
+    <row r="46" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="47" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1529,26 +1500,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="H43:J43"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="H44:J44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B32:J32"/>
     <mergeCell ref="B33:J33"/>
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1573,10 +1544,7 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I17:J25"/>
+    <mergeCell ref="I17:J24"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>14/07/2025</t>
+    <t>05/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>b</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,9 +59,6 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>SUR</t>
-  </si>
-  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -83,49 +80,10 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Laptop</t>
+    <t>Teclado</t>
   </si>
   <si>
     <t>DELL</t>
-  </si>
-  <si>
-    <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>1446MG00C698</t>
-  </si>
-  <si>
-    <t>Y8GS78BY8</t>
-  </si>
-  <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>K120</t>
-  </si>
-  <si>
-    <t>1446MG0C698O</t>
-  </si>
-  <si>
-    <t>MK235</t>
-  </si>
-  <si>
-    <t>2134MR38A788</t>
   </si>
   <si>
     <t>KB216T</t>
@@ -855,7 +813,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -994,7 +952,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -1003,7 +961,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1052,24 +1010,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1080,17 +1038,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1099,14 +1057,22 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="51" t="s">
+      <c r="B18" s="53">
+        <v>2</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="53" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
+      <c r="G18" s="53" t="s">
+        <v>27</v>
+      </c>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
@@ -1115,181 +1081,134 @@
     <row r="19" spans="1:11">
       <c r="A19" s="52"/>
       <c r="B19" s="53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="52"/>
-      <c r="B20" s="53">
-        <v>3</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="53" t="s">
+    <row r="20" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A20" s="18"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="31"/>
+    </row>
+    <row r="21" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A21" s="18"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="31"/>
+    </row>
+    <row r="22" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A23" s="19"/>
+      <c r="B23" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:11" customHeight="1" ht="9">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A25" s="20"/>
+      <c r="B25" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53" t="s">
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+    </row>
+    <row r="26" spans="1:11" customHeight="1" ht="15">
+      <c r="A26" s="20"/>
+      <c r="B26" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="52"/>
-      <c r="B21" s="53">
-        <v>4</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="53" t="s">
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15">
+      <c r="A27" s="20"/>
+      <c r="B27" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="15">
+      <c r="A28" s="20"/>
+      <c r="B28" s="27" t="s">
         <v>36</v>
-      </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="52"/>
-      <c r="B22" s="53">
-        <v>5</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="52"/>
-      <c r="B23" s="53">
-        <v>6</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="52"/>
-      <c r="B24" s="53">
-        <v>7</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A25" s="18"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="31"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="18"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="31"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="19"/>
-      <c r="B28" s="33" t="s">
-        <v>46</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -1300,23 +1219,23 @@
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
     </row>
-    <row r="29" spans="1:11" customHeight="1" ht="9">
+    <row r="29" spans="1:11" customHeight="1" ht="15">
       <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="20"/>
-      <c r="B30" s="27" t="s">
-        <v>47</v>
-      </c>
+      <c r="B29" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+    </row>
+    <row r="30" spans="1:11" customHeight="1" ht="12">
+      <c r="A30" s="21"/>
+      <c r="B30" s="28"/>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
@@ -1326,10 +1245,10 @@
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15">
-      <c r="A31" s="20"/>
-      <c r="B31" s="27" t="s">
-        <v>48</v>
+    <row r="31" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A31" s="17"/>
+      <c r="B31" s="29" t="s">
+        <v>38</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1340,152 +1259,84 @@
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15">
-      <c r="A32" s="20"/>
-      <c r="B32" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15">
-      <c r="A33" s="20"/>
-      <c r="B33" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15">
-      <c r="A34" s="20"/>
-      <c r="B34" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="26"/>
+    <row r="32" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="25" t="s">
+        <v>39</v>
+      </c>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
+      <c r="H34" s="34" t="s">
+        <v>40</v>
+      </c>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:11" customHeight="1" ht="12">
-      <c r="A35" s="21"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-    </row>
-    <row r="36" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A36" s="17"/>
-      <c r="B36" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-    </row>
+    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="36" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+    </row>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+      <c r="C38" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="H38" s="25" t="str">
+        <f>C8</f>
+        <v>Alan Bauza Valdez</v>
+      </c>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
       <c r="C39" s="25" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
-      <c r="H39" s="34" t="s">
-        <v>54</v>
+      <c r="H39" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="I39" s="26"/>
       <c r="J39" s="26"/>
     </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C43" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="H43" s="25" t="str">
-        <f>C8</f>
-        <v>Alan Bauza Valdez</v>
-      </c>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-    </row>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C44" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="H44" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-    </row>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-    </row>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="47" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+    </row>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1500,26 +1351,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="H38:J38"/>
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="H39:J39"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
     <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:J36"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1529,22 +1380,7 @@
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I17:J24"/>
+    <mergeCell ref="I17:J19"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>29/09/2025</t>
+    <t>20/01/2026</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>xturfghj</t>
+    <t>qwert</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>ctvybuoi</t>
+    <t>asdfghj</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -143,7 +143,7 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
+    <t>Alejandro Cancino Argüello</t>
   </si>
   <si>
     <t>Coordinador de TI</t>

--- a/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
+++ b/database/controller_excel/Resguardo_Alan_Bauza_Valdez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>20/01/2026</t>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>qwert</t>
+    <t>ew</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,9 +59,6 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>asdfghj</t>
-  </si>
-  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -83,37 +80,58 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Teclado</t>
+    <t>Laptop</t>
   </si>
   <si>
     <t>DELL</t>
   </si>
   <si>
-    <t>KB216T</t>
-  </si>
-  <si>
-    <t>CN-0F2JV2-LO300-0CE-00LV-A04</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>MS116T1</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-150-08Y0</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>23-08-69698</t>
+    <t>Latitude 5540</t>
+  </si>
+  <si>
+    <t>4JHNF14</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00191</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0723JG-LOC00-413-0EY3-A01</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FLX</t>
+  </si>
+  <si>
+    <t>Puerto Replicador USB</t>
+  </si>
+  <si>
+    <t>3005P USB</t>
+  </si>
+  <si>
+    <t>7CB824A373</t>
+  </si>
+  <si>
+    <t>Cargador de Adaptador usb</t>
+  </si>
+  <si>
+    <t>677777-003</t>
+  </si>
+  <si>
+    <t>WCNXF0AAR4QHBX</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -143,10 +161,10 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Alejandro Cancino Argüello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI y Telemetría</t>
   </si>
   <si>
     <t>Supervisor Operaciones</t>
@@ -816,7 +834,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -955,7 +973,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -964,7 +982,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1013,24 +1031,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1041,41 +1059,35 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
+      <c r="I17" s="53" t="s">
+        <v>10</v>
+      </c>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>27</v>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
+        <v>25</v>
       </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>28</v>
-      </c>
+      <c r="G18" s="53"/>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
@@ -1084,106 +1096,135 @@
     <row r="19" spans="1:11">
       <c r="A19" s="52"/>
       <c r="B19" s="53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A20" s="18"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="18"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="31"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
+    <row r="20" spans="1:11">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53">
+        <v>3</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>4</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>5</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
     </row>
     <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="19"/>
-      <c r="B23" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="9">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="31"/>
+    </row>
+    <row r="24" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A24" s="18"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="31"/>
     </row>
     <row r="25" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A25" s="20"/>
-      <c r="B25" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
-        <v>35</v>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A26" s="19"/>
+      <c r="B26" s="33" t="s">
+        <v>39</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1194,24 +1235,22 @@
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
     </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
+    <row r="27" spans="1:11" customHeight="1" ht="9">
       <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="15.75">
       <c r="A28" s="20"/>
       <c r="B28" s="27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -1225,7 +1264,7 @@
     <row r="29" spans="1:11" customHeight="1" ht="15">
       <c r="A29" s="20"/>
       <c r="B29" s="27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1236,9 +1275,11 @@
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="1:11" customHeight="1" ht="12">
-      <c r="A30" s="21"/>
-      <c r="B30" s="28"/>
+    <row r="30" spans="1:11" customHeight="1" ht="15">
+      <c r="A30" s="20"/>
+      <c r="B30" s="27" t="s">
+        <v>42</v>
+      </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
@@ -1248,10 +1289,10 @@
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A31" s="17"/>
-      <c r="B31" s="29" t="s">
-        <v>39</v>
+    <row r="31" spans="1:11" customHeight="1" ht="15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1262,84 +1303,124 @@
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="25" t="s">
-        <v>40</v>
-      </c>
+    <row r="32" spans="1:11" customHeight="1" ht="15">
+      <c r="A32" s="20"/>
+      <c r="B32" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+    </row>
+    <row r="33" spans="1:11" customHeight="1" ht="12">
+      <c r="A33" s="21"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A34" s="17"/>
+      <c r="B34" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="26"/>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
-      <c r="H34" s="34" t="s">
-        <v>41</v>
-      </c>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="35" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+    </row>
     <row r="36" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C38" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="H38" s="25" t="str">
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="H37" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="39" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C41" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="H41" s="25" t="str">
         <f>C8</f>
         <v>Alan Bauza Valdez</v>
       </c>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C39" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="H39" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+    </row>
     <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="C42" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="H42" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+    </row>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+    </row>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="45" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1354,26 +1435,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="H42:J42"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B34:J34"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1383,7 +1464,16 @@
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I17:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I17:J22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
